--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-07_approval_steps_承認ステップ_テーブル詳細設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-07_approval_steps_承認ステップ_テーブル詳細設計書.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:C22"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -563,6 +563,8 @@
     <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="1" t="inlineStr">
         <is>
@@ -577,6 +579,8 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -645,7 +649,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -685,12 +689,14 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-003 は全 9 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち approval_steps を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
-列・型・NULL・既定値・制約・索引・トリガは backend/schema.sql（KF-DD-003 v2.0 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜022 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
-章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications）のみ作成している。</t>
+          <t>本書の位置づけ：KF-DD-003 は全 10 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち approval_steps を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
+列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration の V1__init_schema.sql・V4__attendance_breaks.sql・V5__break_correction_request.sql（Flyway。KF-DD-003 v2.3 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）に、2026/10/05 のコード（AttendanceService / RequestService / ApprovalService / DepartmentController）から起こした ONL-024〜026（休憩・離席の開始・終了、部署一覧。番号は仮）と既存処理の追加アクセスを重ね、BAT-001〜003 と合わせて抽出した。
+章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications / attendance_breaks）のみ作成している。</t>
         </is>
       </c>
     </row>
@@ -713,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K32"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -729,6 +735,7 @@
     <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -746,7 +753,7 @@
       <c r="J2" s="9" t="n"/>
       <c r="K2" s="10" t="n"/>
     </row>
-    <row r="3" ht="48.5" customHeight="1">
+    <row r="3" ht="63" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t>前提</t>
@@ -754,8 +761,8 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>申請 1（山田の年休、承認待ち・1段目）、申請 2（鈴木の半休、承認済み）、申請 3（山田の打刻修正、1段目で差戻し）の各ステップ。
-例の INSERT は schema.sql 実行直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
+          <t>申請 1（山田の年休、承認待ち・1段目）、申請 2（鈴木の半休、承認済み）、申請 3（山田の打刻修正、1段目で差戻し）の各ステップ。（申請 4＝鈴木の下書き、申請 5＝山田の休憩・離席修正の下書きは未提出のためステップなし。種別が BREAK_CORRECTION でもステップの作り方は同じ）
+例の INSERT は V1〜V5 適用直後の DB（開発用シードを入れていない状態）に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → attendance_breaks → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -768,6 +775,7 @@
       <c r="J3" s="9" t="n"/>
       <c r="K3" s="10" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
@@ -1031,7 +1039,7 @@
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="10" t="n"/>
     </row>
-    <row r="12" ht="48.5" customHeight="1">
+    <row r="12" ht="63" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>6</t>
@@ -1054,7 +1062,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>WAITING（申請は RETURNED のため以後処理されない）</t>
+          <t>WAITING（申請は RETURNED のため以後処理されない。API の表示は SKIPPED）</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1072,6 +1080,7 @@
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="10" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
@@ -1236,6 +1245,7 @@
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="10" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
@@ -1398,6 +1408,7 @@
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="10" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
@@ -1514,7 +1525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1525,6 +1536,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -1604,12 +1616,12 @@
     <row r="7" ht="48.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>バックアップ（BAT-003）</t>
+          <t>API の SKIPPED 表示</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。</t>
+          <t>画面・API で『処理なし』と表示されるステップも DB 上は WAITING。DB を直接集計・照会する場合は requests.status='PENDING' AND current_step = step_no を併用する（課題 AS-1）。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -1617,15 +1629,15 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="48.5" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>マイグレーション</t>
+          <t>バックアップ（BAT-003）</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>現状は schema.sql（set_updated_at 関数・トリガを含む）の手動実行＋ spring.jpa.hibernate.ddl-auto=validate。列追加・索引追加は ALTER 文を別ファイルにし、将来 Flyway（V1__baseline.sql ＋ V2__… ）へ移行する（KF-DD-003 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。なお BAT-001〜003 は設計のみで、現行の backend には実装が無い（@Scheduled・pg_dump 呼び出しなし）。</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
@@ -1633,79 +1645,64 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="9" ht="48.5" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>マイグレーション</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Flyway（V1__init_schema.sql：set_updated_at 関数・トリガ・初期データを含む／V2・V3：祝日の初期データ／V4：attendance_breaks の追加／V5：requests への休憩・離席修正の 3 列と制約の追加）＋ spring.jpa.hibernate.ddl-auto=validate。V1〜V5 は適用後に編集せず、列追加・索引追加は次の版 V6__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>9.2 既知課題・未決事項（未解決のもの。解消済みは 9.2b）</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>推奨対応</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>優先度</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="77.5" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>C-3</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>先頭の DROP TABLE ... CASCADE（開発用）、DDL、トリガ／関数、初期データ（休暇種別 11 件・部署 3 件）が 1 ファイルに同居している。ヘッダは『PostgreSQL 18／KF-DD-003 v2.0』に修正済みで、旧『H2 / PostgreSQL 共通』の記述は解消。</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>本番 DB で誤実行すると全データを失う。</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql を DDL 本体（DROP なし）／ dev-reset.sql（DROP）／ seed（初期データ）に分割。将来 Flyway（V1__baseline.sql）へ移行。</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1770,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="63" customHeight="1">
+    <row r="15" ht="77.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>C-6</t>
@@ -1786,7 +1783,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+          <t>JST 固定は Hikari の connection-init-sql に依存する（Flyway はアプリの DataSource＝Hikari で実行するため JST）。psql での手動 SQL、BAT-003（設計）の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1805,404 +1802,430 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="63" customHeight="1">
+    <row r="16" ht="106.5" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
+          <t>C-7</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>保存期間 5 年を超えたデータの自動削除・アーカイブが未実装</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>KF-RD-002 §9（決定 6）は勤怠・申請・監査ログの保存期間を 5 年（設定値）とし、BAT-005『監査ログ／履歴の保存期間管理（アーカイブ）』を計画している。現行の backend には削除・アーカイブ処理も保存期間の設定値も無く、業務データは物理削除しない（例外は通知・祝日・再提出時の承認ステップ）。</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>運用開始から 5 年間は影響しない。5 年を超えた後の扱い（残す／消す・退避）の手順が無く、運用者の判断になる。件数は 5 年で 5 表合計（attendance_breaks 約 75 万行を含む）約 120 万行規模で、容量・性能上の問題にはなりにくい。</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>運用開始（2026 年）の 5 年後（2031 年）までに、BAT-005 の設計・実装、または手動の退避 SQL の手順を決める。それまでは『消さずに保持する』方針で運用する（5 年はこの方針の目安）。</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="63" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>R-6</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>承認ルート確定後の上長変更・無効化への追従が無い</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>承認ルート確定後に users.manager_id が変わっても approval_steps.approver_id は変わらない。1段目の上長が INACTIVE になった場合の代理承認は未対応（ONL-005/010）。</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>承認待ちのまま止まる申請が発生しうる。</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>承認者付替えの管理機能（ONL-014 将来課題）。10章 SQL「承認者が無効な待ち」で検出。</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="77.5" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="18" ht="121" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>AS-1</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>WITHDRAWN 等の終了申請に WAITING のステップが残る</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>ONL-008 は approval_steps を更新しない。ONL-011/012 の SQL は処理した 1 ステップのみ更新し、他段を更新しない。例：1段目で却下すると 2段目は WAITING のまま。</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>ONL-008 は approval_steps を更新しない。ONL-011/012 の SQL は処理した 1 ステップのみ更新し、他段を更新しない。例：1段目で却下すると 2段目は WAITING のまま。API の応答（ONL-007 の承認履歴）は、PENDING でない申請の WAITING を SKIPPED（処理なし）と表示するが、これは RequestService#displayStatus の表示変換で DB の値は WAITING のまま。</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>approval_steps.status = 'WAITING' だけでは「処理待ち」を意味しない。必ず requests.status='PENDING' AND current_step = step_no と併用する（ONL-009 は実施済み）。集計・バッチで誤用しやすい。</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>方針を明文化（現行の維持）。もしくは終端時に未処理ステップを CANCELLED 等へ更新（コード値追加）。</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>方針を明文化（現行の維持。画面上の誤解は SKIPPED 表示で緩和済み）。DB 側でも区別したい場合は、終端時に未処理ステップを CANCELLED 等へ更新（コード値追加）。</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="48.5" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19" ht="48.5" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>AS-2</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>ck_as_step が 1,2 固定で 3 段以上に拡張できず、整合 CHECK も無い</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>step_no IN (1,2) は固定。status='WAITING' ⇔ acted_at IS NULL、WAITING 以外は acted_at が必須、といった整合を DB は保証しない。</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>承認段数を増やすと DDL 変更が必要。acted_at 欠落データが入りうる。</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>ck_as_step を step_no BETWEEN 1 AND 9 等へ緩和するか現状維持を決定。ck_as_acted を追加。</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="92" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="20" ht="92" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>AS-3</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>再提出で差戻しコメントなどの承認履歴が失われる</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>ONL-022 は再提出時に旧 approval_steps を全て DELETE して作り直す（uq(request_id, step_no) のため INSERT し直す）。差戻しコメント・処理者・処理日時を含む前回の履歴は DB に残らず、ONL-007 の承認履歴には再提出後のステップのみが出る。</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>承認履歴（コメント・処理者）の喪失。監査・紛争時に追えない。</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>approval_histories（ステップ処理の追記専用ログ）を追加するか、再提出ごとに submit_no を持たせる。</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="63" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21" ht="63" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>AS-4</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>approver_id の索引は 2段目（NULL）検索に最適でない</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>ONL-009 の承認待ち検索は (1段目 approver_id = 自分) OR (2段目 かつ ADMIN) の OR 条件で、idx_as_approver (approver_id, status) だけでは 2段目を絞り込めない。</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>WAITING が累積すると走査が増える（年 10,000 行までは問題なし）。</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>(step_no, status) WHERE status='WAITING' の部分索引を追加。</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="77.5" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="22" ht="77.5" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>AS-5</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>ONL-022 規格が存在しない索引 idx_as_request を参照している</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>ONL-022 の deleteByRequestId の備考に『idx_as_request（request_id）を利用』とあるが、schema.sql に該当索引は無い。実際は uq_approval_steps_1 (request_id, step_no) の先頭列が使われる（追加索引は不要）。</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>ONL-022 の deleteByRequestId の備考に『idx_as_request（request_id）を利用』とあるが、V1__init_schema.sql に該当索引は無い。実際は uq_approval_steps_1 (request_id, step_no) の先頭列が使われる（追加索引は不要）。</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>設計書と DDL の不一致（実害なし）。</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>ONL-022 規格の記載を uq_approval_steps_1 に修正する。</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>9.2b 解消済み（v2.0）の課題（履歴。この版で対応済み）</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>解消内容</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>根拠（DDL／規格）</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>残る事項</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="106.5" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="26" ht="106.5" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>C-1</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>updated_at が更新時に自動更新されない</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>V1 の全 9 表（V4 の attendance_breaks にも同様）に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="92" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="27" ht="135.5" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>C-2</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。業務時刻は Clock（ClockConfig / AppTime。Asia/Tokyo 固定）から取得した LocalDateTime をそのまま保存する。hibernate.jdbc.time_zone は設定していない（application.properties に無い）。Docker では ENV TZ=Asia/Tokyo。</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>アプリ以外の接続は対象外（課題 C-6）。</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="92" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="28" ht="135.5" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>C-3</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="92" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>R-1</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>下書き提出・差戻し後の再提出を行う ONL が存在しない</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>ONL-022（POST /api/requests/{id}/submit）を追加。DRAFT / RETURNED → PENDING。ONL-005 と同じ検証（E-004 / E-005）、LEAVE は days を再計算、旧 approval_steps を全て削除して作り直す（uq(request_id, step_no) 対策にバルク DELETE）、現在の承認者へ REQUEST_SUBMITTED 通知。</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>下書きの内容を更新する API（課題 R-7）と、再提出で承認履歴が消える点（課題 AS-3）が残る。</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>requests, approval_steps</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>9.3 ONL 規格が挙げた既知の制約・未対応（この表を使う処理の security 欄から抜粋）</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>処理ID</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>内容（原文抜粋）</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="10" t="n"/>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>ONL-005</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>既知の制約</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>承認ルート確定後に上長が変更されても既存申請の approver_id は変わらない。管理者が1人のみで、その管理者自身が申請すると承認者がいなくなる（運用で別の管理者を用意する）。通知は type / request_id を持つため、画面は requestId があれば SCR-106 の該当申請へ遷移する（ONL-019）。</t>
-        </is>
-      </c>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="10" t="n"/>
     </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>ONL-007</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>既知の制約</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>権限判定のためロールは users.role の最新値を参照するため、閲覧者が ADMIN でも承認者でもない場合は users を1回余分に読む。部署・種別の変更履歴は保持していないため、過去申請でも現在の名称で表示される。</t>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>処理ID</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>内容（原文抜粋）</t>
         </is>
       </c>
       <c r="D32" s="9" t="n"/>
@@ -2212,7 +2235,7 @@
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>ONL-008</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -2222,7 +2245,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>取下げ日時は updated_at（DB トリガ）で参照できるが、取下げ者の個別記録はない（本人のみが取下げ可能なため申請者と同一）。DRAFT / RETURNED の取下げでは通知しない。承認済み（APPROVED）の申請の取消は本 API の対象外。</t>
+          <t>承認ルート確定後に上長が変更されても既存申請の approver_id は変わらない。管理者が1人のみで、その管理者自身が申請すると承認者がいなくなる（運用で別の管理者を用意する）。通知は type / request_id を持つため、画面は requestId があれば SCR-106 の該当申請へ遷移する（ONL-019）。</t>
         </is>
       </c>
       <c r="D33" s="9" t="n"/>
@@ -2232,27 +2255,27 @@
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>既知の制約（今後）</t>
+          <t>既知の制約</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>承認・差戻し・却下の操作履歴を残す監査ログ、承認者の代理設定、1段目の上長が INACTIVE になった場合の代理承認、1名の管理者が全段を承認する運用の制限。有効な ADMIN がいない場合、2段目は誰も処理できない。</t>
+          <t>権限判定のためロールは users.role の最新値を参照するため、閲覧者が ADMIN でも承認者でもない場合は users を1回余分に読む。部署・種別の変更履歴は保持していないため、過去申請でも現在の名称で表示される。</t>
         </is>
       </c>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="10" t="n"/>
     </row>
-    <row r="35" ht="48.5" customHeight="1">
+    <row r="35" ht="34" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>ONL-022</t>
+          <t>ONL-008</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -2262,31 +2285,72 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>再提出で前回の承認履歴（差戻しコメントを含む）が削除される。下書きの内容を更新する API（PUT）は未定義のため、内容を直したい場合は新規申請になる（今後の課題）。上長が変更されていれば、再提出時の承認ルートは新しい上長で作り直される。管理者が 1 人のみで本人が申請者の場合は承認者がいなくなる（ONL-005 と同じ運用制約）。</t>
+          <t>取下げ日時は updated_at（DB トリガ）で参照できるが、取下げ者の個別記録はない（本人のみが取下げ可能なため申請者と同一）。DRAFT / RETURNED の取下げでは通知しない。承認済み（APPROVED）の申請の取消は本 API の対象外。</t>
         </is>
       </c>
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="9" t="n"/>
       <c r="F35" s="10" t="n"/>
     </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約（今後）</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>承認・差戻し・却下の操作履歴を残す監査ログ、承認者の代理設定、1段目の上長が INACTIVE になった場合の代理承認、1名の管理者が全段を承認する運用の制限。有効な ADMIN がいない場合、2段目は誰も処理できない。</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="48.5" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>ONL-022</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>再提出で前回の承認履歴（差戻しコメントを含む）が削除される。下書きの内容を更新する API（PUT）は未定義のため、内容を直したい場合は新規申請になる（今後の課題）。上長が変更されていれば、再提出時の承認ルートは新しい上長で作り直される。管理者が 1 人のみで本人が申請者の場合は承認者がいなくなる（ONL-005 と同じ運用制約）。</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="C36:F36"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C34:F34"/>
-    <mergeCell ref="A23:F23"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C32:F32"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2300,7 +2364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2311,6 +2375,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -2365,13 +2430,13 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>step 1・2 の件数が同数（提出済み申請ごとに 2 行）</t>
+          <t>step 1 の件数は step 2 以下（提出済み申請ごとに step 2 は 1 行、step 1 は上長ありの申請のみ）</t>
         </is>
       </c>
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="10" t="n"/>
     </row>
-    <row r="5" ht="48.5" customHeight="1">
+    <row r="5" ht="63" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>2</t>
@@ -2379,17 +2444,17 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>ステップが 2 行でない提出済み申請（欠落・過剰）</t>
+          <t>ステップの欠落・過剰がある提出済み申請（2段目が無い・3 行以上・1 行だけで 2段目でない）</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>SELECT r.id, COUNT(s.id) FROM requests r LEFT JOIN approval_steps s ON s.request_id = r.id WHERE r.status &lt;&gt; 'DRAFT' GROUP BY r.id HAVING COUNT(s.id) &lt;&gt; 2;</t>
+          <t>SELECT r.id, COUNT(s.id), MIN(s.step_no) FROM requests r LEFT JOIN approval_steps s ON s.request_id = r.id WHERE r.status &lt;&gt; 'DRAFT' GROUP BY r.id HAVING COUNT(s.id) NOT IN (1, 2) OR (COUNT(s.id) = 1 AND MIN(s.step_no) &lt;&gt; 2);</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>0 行</t>
+          <t>0 行（上長あり＝2 行、上長なし・無効＝2段目のみの 1 行）</t>
         </is>
       </c>
       <c r="E5" s="9" t="n"/>
@@ -2547,40 +2612,65 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>updated_at トリガ trg_approval_steps_updated_at が存在し有効であること</t>
+          <t>DB に SKIPPED などの表示用の値が入っていないこと</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>SELECT tgname, tgenabled FROM pg_trigger WHERE tgrelid = 'approval_steps'::regclass AND NOT tgisinternal;</t>
+          <t>SELECT status, COUNT(*) FROM approval_steps WHERE status NOT IN ('WAITING','APPROVED','RETURNED','REJECTED') GROUP BY status;</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1 行（trg_approval_steps_updated_at、tgenabled = 'O'＝有効）。0 行だと updated_at が更新されない</t>
+          <t>0 行（ck_as_status で拒否される。SKIPPED は API の応答にだけ現れる）</t>
         </is>
       </c>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>全 SQL を PostgreSQL 16 上で schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>updated_at トリガ trg_approval_steps_updated_at が存在し有効であること</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>SELECT tgname, tgenabled FROM pg_trigger WHERE tgrelid = 'approval_steps'::regclass AND NOT tgisinternal;</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>1 行（trg_approval_steps_updated_at、tgenabled = 'O'＝有効）。0 行だと updated_at が更新されない</t>
+        </is>
+      </c>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="10" t="n"/>
     </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>全 SQL を PostgreSQL 16 上で V1〜V5 のマイグレーション（V1 は v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D13:F13"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D3:F3"/>
@@ -2602,7 +2692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2639,7 +2729,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="63" customHeight="1">
+    <row r="2" ht="68" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -2661,6 +2751,52 @@
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>V2 追加に伴いデータ例の前提を更新。保存期間 5 年の自動削除・アーカイブは未実装であることを課題 C-7 として追加。</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="158" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>コードと突合して更新。①表示状態 SKIPPED は API 層の変換（RequestService#displayStatus。申請が承認待ちでないのに WAITING のまま残るステップの表示）であり、DB の status は WAITING / APPROVED / RETURNED / REJECTED の 4 値のまま変わらないことを 1章・2章・4.4・運用・確認 SQL に明記（課題 AS-1 を更新）②休憩・離席修正申請（BREAK_CORRECTION。V5）も同じ 2 段承認であることを追記（列・制約に変更なし）③承認ルートの記述を訂正（上長なし・無効の場合は 1段目の行を作らず 2段目のみ。従来『上長なしは approver_id=NULL』と記載）④8章の説明に、下書き（申請 4・5）はステップを持たないことを追記。</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2675,7 +2811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F36"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2686,6 +2822,7 @@
     <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -2714,7 +2851,7 @@
       <c r="E3" s="9" t="n"/>
       <c r="F3" s="10" t="n"/>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="63" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>用途</t>
@@ -2722,7 +2859,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>申請ごとの承認の各段（1段目＝上長、2段目＝管理者）を 1 行ずつ持つ。段ごとの状態・承認者・コメント・処理日時を保存し、承認待ち一覧（ONL-009）、承認/差戻し/却下（ONL-010〜012）、申請詳細の承認履歴（ONL-007）で使う。</t>
+          <t>申請ごとの承認の各段（1段目＝上長、2段目＝管理者）を 1 行ずつ持つ（上長なし・無効の場合は 2段目のみの 1 行）。段ごとの状態・承認者・コメント・処理日時を保存し、承認待ち一覧（ONL-009）、承認/差戻し/却下（ONL-010〜012）、申請詳細の承認履歴（ONL-007）で使う。 休憩・離席修正申請（BREAK_CORRECTION）を含む全ての申請種別で同じ 2 段承認。なお API・画面は、終了した申請に残った WAITING を SKIPPED（処理なし）と表示するが、これは API 層の表示変換で DB の値は変わらない（4.4）。</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -2738,7 +2875,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>PostgreSQL 18 / UTF-8。DDL の正は backend/schema.sql。</t>
+          <t>PostgreSQL 18 / UTF-8。DDL の正は Flyway のマイグレーション（backend/src/main/resources/db/migration の V1__init_schema.sql）。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -2890,6 +3027,7 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
@@ -3150,6 +3288,7 @@
       </c>
       <c r="F26" s="10" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
@@ -3255,7 +3394,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>ONL-001〜022 の概要</t>
+          <t>ONL-001〜022 の概要（ONL-023 以降は個別のオンライン詳細設計書）</t>
         </is>
       </c>
       <c r="D33" s="9" t="n"/>
@@ -3302,10 +3441,10 @@
       <c r="E35" s="9" t="n"/>
       <c r="F35" s="10" t="n"/>
     </row>
-    <row r="36" ht="19.5" customHeight="1">
+    <row r="36" ht="106.5" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>backend/schema.sql</t>
+          <t>backend/src/main/resources/db/migration/V1__init_schema.sql・V4__attendance_breaks.sql・V5__break_correction_request.sql</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -3315,7 +3454,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>本書の自動生成元</t>
+          <t>本書の自動生成元（V2・V3 は祝日の初期データのみ）</t>
         </is>
       </c>
       <c r="D36" s="9" t="n"/>
@@ -3370,7 +3509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:M13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3388,10 +3527,11 @@
     <col width="40" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>2.1 列定義（schema.sql から自動生成）</t>
+          <t>2.1 列定義（db/migration の V1・V4・V5 から自動生成。物理列順）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -3654,7 +3794,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>ONL-005 / ONL-022 が 1・2 を作成（ApprovalRouteService#createSteps）。1段目＝上長、2段目＝管理者。</t>
+          <t>ONL-005 / ONL-022 が 1・2 を作成（ApprovalRouteService#createSteps。申請種別 LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION とも同じ）。1段目＝上長、2段目＝管理者。</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -3718,7 +3858,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>1段目：ONL-005 / ONL-022 が作成時に users.manager_id を設定（上長なしは NULL）。2段目：作成時 NULL。処理時（ONL-010〜012）に実際に処理した人の users.id で上書き。</t>
+          <t>1段目：ONL-005 / ONL-022 が作成時に users.manager_id（有効な上長）を設定。上長なし・無効（INACTIVE）・自己参照の場合は 1段目の行を作らない。2段目：作成時 NULL。処理時（ONL-010〜012）に実際に処理した人の users.id で上書き。</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -3781,12 +3921,12 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>ステップ状態。WAITING／APPROVED／RETURNED／REJECTED。</t>
+          <t>ステップ状態。DB の値は WAITING／APPROVED／RETURNED／REJECTED の 4 つのみ。申請が承認待ちでないのに WAITING のまま残ったステップは、API の応答だけ SKIPPED（処理なし）と表示する（表示用の変換で DB は変えない。4.4）。</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>ONL-005 / ONL-022 が WAITING で作成。ONL-010/011/012 の actIfWaiting が APPROVED/RETURNED/REJECTED へ（WHERE status='WAITING' の条件付き UPDATE）。</t>
+          <t>ONL-005 / ONL-022 が WAITING で作成。ONL-010/011/012 の actIfWaiting が APPROVED/RETURNED/REJECTED へ（WHERE status='WAITING' の条件付き UPDATE）。DB に保存する値はこの 4 つだけで、SKIPPED は API の応答時にだけ作る表示用の値（RequestService#displayStatus。4.4）。</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -4029,7 +4169,7 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
+          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値はマイグレーション（V1・V4・V5）の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
         </is>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -4062,7 +4202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4073,10 +4213,11 @@
     <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>3.1 制約一覧（schema.sql の定義名のまま）</t>
+          <t>3.1 制約一覧（マイグレーションの定義名のまま）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -4357,6 +4498,7 @@
       </c>
       <c r="F12" s="10" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
@@ -4491,7 +4633,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>CREATE INDEX（schema.sql）</t>
+          <t>CREATE INDEX（V1__init_schema.sql）</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -4508,6 +4650,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
@@ -4600,10 +4743,11 @@
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="10" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>3.4 推奨する変更（schema.sql は変更しない。提案のみ。DDL は schema.sql＋8章データに対して実行確認済み）</t>
+          <t>3.4 推奨する変更（適用済みのマイグレーションは変更しない。提案のみ。DDL は V1〜V5＋8章データに対して実行確認済み）</t>
         </is>
       </c>
       <c r="B27" s="9" t="n"/>
@@ -4720,7 +4864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F21"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4731,6 +4875,7 @@
     <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -4883,6 +5028,7 @@
       </c>
       <c r="F7" s="10" t="n"/>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
@@ -4923,7 +5069,7 @@
       </c>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="19.5" customHeight="1">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>（新規）</t>
@@ -4936,7 +5082,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>WAITING（step 1・2 とも）</t>
+          <t>WAITING（step 1・2。上長なし・無効は step 2 のみ）</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -5091,6 +5237,7 @@
       </c>
       <c r="F16" s="10" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
@@ -5145,7 +5292,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>上長なしの場合 approver_id=NULL・current_step=2 で開始</t>
+          <t>上長なし・無効の場合は 1段目の行を作らず、2段目のみで current_step=2 から開始</t>
         </is>
       </c>
       <c r="E20" s="9" t="n"/>
@@ -5175,25 +5322,155 @@
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="10" t="n"/>
     </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>4.4 API・画面の表示状態 SKIPPED（DB の値ではない）</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>表示（API の status）</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>DB の status</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>変換する条件</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>変換する処理</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>WAITING</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>WAITING</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>申請が PENDING（承認待ち）</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>変換しない</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>処理待ち（current_step のステップが処理対象）</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="77.5" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>WAITING（変更しない）</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>申請が PENDING 以外（RETURNED / REJECTED / WITHDRAWN / APPROVED）で、ステップが WAITING のまま</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>RequestService#displayStatus（toSteps。申請詳細 ONL-007 の承認履歴 StepDetail）</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>『承認待ち』と誤解させないための表示のみ。DB の status・acted_at は更新しない（updated_at も変わらない）。例：1段目で差戻し・却下した申請の 2段目、取り下げた申請の未処理のステップ。SKIPPED を条件にした検索・集計は DB に対しては行えず、requests.status と併用する（課題 AS-1）</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>APPROVED / RETURNED / REJECTED</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>同じ値</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>変換しない</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>処理済みのステップ</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="23">
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="D20:F20"/>
     <mergeCell ref="D19:F19"/>
     <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D20:F20"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5208,7 +5485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5219,6 +5496,7 @@
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -5327,6 +5605,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
@@ -5383,6 +5662,7 @@
       <c r="E9" s="7" t="inlineStr"/>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
@@ -5411,6 +5691,7 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
@@ -5463,7 +5744,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>整合性をアプリで守る点：(1) 提出済みの申請に必ず step 1・2 の 2 行（再提出は旧行削除→再作成）、(2) 処理できるのは requests.status='PENDING' かつ current_step = step_no のとき（ONL-009 の検索条件、ONL-010〜012 の更新条件）、(3) 申請者本人は処理不可（E-009）、(4) 終了した申請に WAITING のステップが残りうる（課題 AS-1）。</t>
+          <t>整合性をアプリで守る点：(1) 提出済みの申請に step 2（管理者）を必ず作成し、上長ありなら step 1 も作成（再提出は旧行削除→再作成）、(2) 処理できるのは requests.status='PENDING' かつ current_step = step_no のとき（ONL-009 の検索条件、ONL-010〜012 の更新条件）、(3) 申請者本人は処理不可（E-009）、(4) 終了した申請に WAITING のステップが残りうる（課題 AS-1）。</t>
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
@@ -5494,7 +5775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5509,6 +5790,7 @@
     <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -5805,6 +6087,7 @@
       <c r="I12" s="9" t="n"/>
       <c r="J12" s="10" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
@@ -6571,7 +6854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6582,6 +6865,7 @@
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -6634,7 +6918,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>uq_approval_steps_1 (request_id, step_no)。ONL-005 は申請 INSERT と同一トランザクションで 2 行を作る。</t>
+          <t>uq_approval_steps_1 (request_id, step_no)。ONL-005 は申請 INSERT と同一トランザクションで 1〜2 行を作る。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -6690,6 +6974,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
@@ -6742,6 +7027,7 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
@@ -6778,7 +7064,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>users → requests → approval_steps → leave_balances / attendance_records → notifications の一方向。逆順で取得しない（ONL-005/008/010〜013/017 の規格で統一）。</t>
+          <t>users → requests → approval_steps → leave_balances / attendance_records → attendance_breaks → notifications の一方向。逆順で取得しない（ONL-005/008/010〜013/017 の規格で統一。休憩・離席の打刻 ONL-024/025 は attendance_records の行ロック → attendance_breaks）。</t>
         </is>
       </c>
       <c r="C16" s="9" t="n"/>
